--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/left/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/left/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.42787</v>
+        <v>16.64145</v>
       </c>
       <c r="D2" t="n">
-        <v>16.43326</v>
+        <v>16.43608</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79821</v>
+        <v>16.46162</v>
       </c>
       <c r="F2" t="n">
-        <v>42.57599</v>
+        <v>41.58393</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05003</v>
+        <v>0.04948</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7826</v>
+        <v>1.81095</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.6662</v>
+        <v>16.52767</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48316</v>
+        <v>16.47102</v>
       </c>
       <c r="E3" t="n">
-        <v>16.35559</v>
+        <v>16.49119</v>
       </c>
       <c r="F3" t="n">
-        <v>41.92613</v>
+        <v>42.17823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04936</v>
+        <v>0.0498</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80908</v>
+        <v>1.79131</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.63535</v>
+        <v>16.79213</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66532</v>
+        <v>16.59081</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43214</v>
+        <v>16.69339</v>
       </c>
       <c r="F4" t="n">
-        <v>41.90662</v>
+        <v>42.38409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04977</v>
+        <v>0.04827</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82675</v>
+        <v>1.78167</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.94905</v>
+        <v>16.53652</v>
       </c>
       <c r="D5" t="n">
-        <v>16.56547</v>
+        <v>16.38681</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48213</v>
+        <v>16.46864</v>
       </c>
       <c r="F5" t="n">
-        <v>42.19078</v>
+        <v>42.30028</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04914</v>
+        <v>0.04992</v>
       </c>
       <c r="H5" t="n">
-        <v>1.77358</v>
+        <v>1.79801</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.44339</v>
+        <v>16.58004</v>
       </c>
       <c r="D6" t="n">
-        <v>16.35937</v>
+        <v>16.32432</v>
       </c>
       <c r="E6" t="n">
-        <v>16.62487</v>
+        <v>16.47382</v>
       </c>
       <c r="F6" t="n">
-        <v>41.63274</v>
+        <v>42.36214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04908</v>
+        <v>0.05054</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79097</v>
+        <v>1.77467</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.79635</v>
+        <v>16.62664</v>
       </c>
       <c r="D7" t="n">
-        <v>16.23654</v>
+        <v>16.52018</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61526</v>
+        <v>16.53461</v>
       </c>
       <c r="F7" t="n">
-        <v>41.65316</v>
+        <v>41.4305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05015</v>
+        <v>0.04978</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81778</v>
+        <v>1.805</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62897</v>
+        <v>16.51624</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51973</v>
+        <v>16.26155</v>
       </c>
       <c r="E8" t="n">
-        <v>16.65157</v>
+        <v>16.49755</v>
       </c>
       <c r="F8" t="n">
-        <v>41.98432</v>
+        <v>41.65124</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05002</v>
+        <v>0.04906</v>
       </c>
       <c r="H8" t="n">
-        <v>1.73963</v>
+        <v>1.77488</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.64939</v>
+        <v>16.52796</v>
       </c>
       <c r="D9" t="n">
-        <v>16.24216</v>
+        <v>16.21489</v>
       </c>
       <c r="E9" t="n">
-        <v>16.37109</v>
+        <v>16.37049</v>
       </c>
       <c r="F9" t="n">
-        <v>41.49211</v>
+        <v>41.83479</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0496</v>
+        <v>0.05032</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80842</v>
+        <v>1.81528</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.56369</v>
+        <v>16.43721</v>
       </c>
       <c r="D10" t="n">
-        <v>16.8467</v>
+        <v>16.43034</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61851</v>
+        <v>16.43307</v>
       </c>
       <c r="F10" t="n">
-        <v>41.1814</v>
+        <v>42.65225</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05012</v>
+        <v>0.05023</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81694</v>
+        <v>1.80133</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59967</v>
+        <v>0.5954</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09845</v>
+        <v>1.12629</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.58952</v>
+        <v>0.59739</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09329</v>
+        <v>1.1032</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6187</v>
+        <v>0.59998</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1062</v>
+        <v>1.10046</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.58406</v>
+        <v>0.60087</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11476</v>
+        <v>1.09477</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.59323</v>
+        <v>0.59332</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10323</v>
+        <v>1.10445</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60693</v>
+        <v>0.60397</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11531</v>
+        <v>1.11229</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59613</v>
+        <v>0.59475</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10668</v>
+        <v>1.09483</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.59537</v>
+        <v>0.6125699999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11805</v>
+        <v>1.10163</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.59977</v>
+        <v>0.60587</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09521</v>
+        <v>1.10966</v>
       </c>
     </row>
   </sheetData>
